--- a/progress.xlsx
+++ b/progress.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,13 +454,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -533,13 +533,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -682,16 +682,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46081</v>
+        <v>46086</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -739,13 +739,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -758,13 +758,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -853,13 +853,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -872,13 +872,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -986,13 +986,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1024,13 +1024,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>3</v>
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>3</v>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1214,13 +1214,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
         <v>2</v>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
         <v>3</v>
@@ -1274,13 +1274,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46081</v>
+        <v>46086</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
         <v>2</v>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
         <v>2</v>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
         <v>2</v>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
@@ -1461,13 +1461,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -1499,16 +1499,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46081</v>
+        <v>46086</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -1518,13 +1518,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
         <v>2</v>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
@@ -1556,13 +1556,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
         <v>2</v>
@@ -1594,13 +1594,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -1616,13 +1616,13 @@
         <v>1</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -1632,13 +1632,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -1670,16 +1670,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46081</v>
+        <v>46086</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -1689,13 +1689,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
         <v>2</v>
@@ -1708,13 +1708,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
         <v>2</v>
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
         <v>5</v>
@@ -1803,13 +1803,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
         <v>1</v>
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
         <v>2</v>
@@ -1860,13 +1860,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
         <v>4</v>
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
         <v>2</v>
@@ -1898,13 +1898,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
         <v>1</v>
@@ -1917,16 +1917,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46081</v>
+        <v>46086</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -1936,13 +1936,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
         <v>4</v>
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
         <v>3</v>
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -1996,13 +1996,13 @@
         <v>1</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2015,13 +2015,13 @@
         <v>1</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
@@ -2053,13 +2053,13 @@
         <v>1</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46081</v>
+        <v>46086</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
         <v>2</v>
@@ -2107,16 +2107,16 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46081</v>
+        <v>46086</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
         <v>2</v>
@@ -2148,13 +2148,13 @@
         <v>1</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -2183,16 +2183,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46081</v>
+        <v>46086</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -2205,13 +2205,13 @@
         <v>1</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -2221,16 +2221,16 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46081</v>
+        <v>46086</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
         <v>2</v>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
         <v>2</v>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
         <v>3</v>
@@ -2297,13 +2297,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
         <v>2</v>
@@ -2316,13 +2316,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
         <v>2</v>
@@ -2338,12 +2338,3774 @@
         <v>1</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E101" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>すこしも（少しも）</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>とても</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ぜんぜん（全然）</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>整理する（せいりする）</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>便利な（べんりな）</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>とりあえず</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>さきほど</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>医療（いりょう）</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2</v>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>どうしても</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2</v>
+      </c>
+      <c r="E110" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>注意（ちゅうい）</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>広い（ひろい）</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>2</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>好調（こうちょう）</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2</v>
+      </c>
+      <c r="E113" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>苦しむ（くるしむ）</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>2</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>技術者（ぎじゅつしゃ）</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>2</v>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>成績（せいせき）</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>2</v>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>修理する（しゅうりする）</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2</v>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>保険（ほけん）</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>性格（せいかく）</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>警告（けいこく）</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>2</v>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>過去（かこ）</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>2</v>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>教育費（きょういくひ）</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>2</v>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>暮らし（くらし）</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>苦手（にがて）</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>細い（ほそい）</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2</v>
+      </c>
+      <c r="E125" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>要求する（ようきゅうする）</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>2</v>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D126" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>大切（たいせつ）</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2</v>
+      </c>
+      <c r="E127" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>生産（せいさん）</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>飛ばす（とばす）</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>暗い（くらい）</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>2</v>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>撮る（とる）</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2</v>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>犯罪（はんざい）</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2</v>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>入る（はいる）</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2</v>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>上げる（あげる）</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2</v>
+      </c>
+      <c r="E134" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>単純な（たんじゅんな）</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ほとんど</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ただちに</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>暑い（あつい）</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>2</v>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D138" t="n">
+        <v>2</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>不十分（ふじゅうぶん）</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>許す（ゆるす）</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>難しい（むずかしい）</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D141" t="n">
+        <v>2</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>好きな（すきな）</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2</v>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D142" t="n">
+        <v>2</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>有名（ゆうめい）</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2</v>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2</v>
+      </c>
+      <c r="E143" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>不自然（ふしぜん）</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>2</v>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>観察（かんさつ）</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>2</v>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D145" t="n">
+        <v>2</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>逃す（のがす）</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2</v>
+      </c>
+      <c r="E146" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>締切（しめきり）</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>2</v>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D147" t="n">
+        <v>2</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>回答（かいとう）</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>2</v>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D148" t="n">
+        <v>2</v>
+      </c>
+      <c r="E148" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>休暇（きゅうか）</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D149" t="n">
+        <v>2</v>
+      </c>
+      <c r="E149" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>見つける（みつける）</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>たとえ</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>紛争（ふんそう）</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>2</v>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D152" t="n">
+        <v>2</v>
+      </c>
+      <c r="E152" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>静か（しずか）</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2</v>
+      </c>
+      <c r="C153" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>増える（ふえる）</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D154" t="n">
+        <v>2</v>
+      </c>
+      <c r="E154" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>探す（さがす）</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D155" t="n">
+        <v>2</v>
+      </c>
+      <c r="E155" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>予定する（よていする）</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D156" t="n">
+        <v>2</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>悲しい（かなしい）</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2</v>
+      </c>
+      <c r="C157" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D157" t="n">
+        <v>2</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>増加する（ぞうかする）</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D158" t="n">
+        <v>2</v>
+      </c>
+      <c r="E158" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>集まる（あつまる）</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>2</v>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2</v>
+      </c>
+      <c r="E159" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>不正確（ふせいかく）</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>2</v>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D160" t="n">
+        <v>2</v>
+      </c>
+      <c r="E160" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>不利（ふり）</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D161" t="n">
+        <v>2</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>続出する（ぞくしゅつする）</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D162" t="n">
+        <v>2</v>
+      </c>
+      <c r="E162" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>得る（える）</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D163" t="n">
+        <v>2</v>
+      </c>
+      <c r="E163" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>経験者（けいけんしゃ）</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>2</v>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D164" t="n">
+        <v>2</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>季節（きせつ）</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D165" t="n">
+        <v>2</v>
+      </c>
+      <c r="E165" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>だからこそ</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D166" t="n">
+        <v>2</v>
+      </c>
+      <c r="E166" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>速い（はやい）</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>2</v>
+      </c>
+      <c r="C167" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D167" t="n">
+        <v>2</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>または</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2</v>
+      </c>
+      <c r="E168" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>理解（りかい）</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>2</v>
+      </c>
+      <c r="C169" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D169" t="n">
+        <v>2</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>降りる（おりる）</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1</v>
+      </c>
+      <c r="C170" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D170" t="n">
+        <v>2</v>
+      </c>
+      <c r="E170" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>調べる（しらべる）</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>2</v>
+      </c>
+      <c r="C171" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D171" t="n">
+        <v>2</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>操作（そうさ）</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>2</v>
+      </c>
+      <c r="C172" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D172" t="n">
+        <v>2</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>報告（ほうこく）</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>2</v>
+      </c>
+      <c r="C173" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D173" t="n">
+        <v>2</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>案内（あんない）</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D174" t="n">
+        <v>2</v>
+      </c>
+      <c r="E174" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>偉い（えらい）</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D175" t="n">
+        <v>2</v>
+      </c>
+      <c r="E175" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>預ける（あずける）</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>2</v>
+      </c>
+      <c r="C176" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>我慢する（がまんする）</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D177" t="n">
+        <v>2</v>
+      </c>
+      <c r="E177" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>回復する（かいふくする）</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>2</v>
+      </c>
+      <c r="C178" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>もちろん</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>1</v>
+      </c>
+      <c r="C179" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2</v>
+      </c>
+      <c r="E179" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>しっかり</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D180" t="n">
+        <v>2</v>
+      </c>
+      <c r="E180" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>平等（びょうどう）</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>丁寧な（ていねいな）</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2</v>
+      </c>
+      <c r="E182" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>講義（こうぎ）</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2</v>
+      </c>
+      <c r="E183" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>応援する（おうえんする）</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>2</v>
+      </c>
+      <c r="C184" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2</v>
+      </c>
+      <c r="E184" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>上がる（あがる）</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
+      <c r="C185" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2</v>
+      </c>
+      <c r="E185" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>守る（まもる）</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2</v>
+      </c>
+      <c r="E186" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>直る（なおる）</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>2</v>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D187" t="n">
+        <v>2</v>
+      </c>
+      <c r="E187" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>捜す（さがす）</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>1</v>
+      </c>
+      <c r="C188" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D188" t="n">
+        <v>2</v>
+      </c>
+      <c r="E188" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>決まる（きまる）</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>2</v>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D189" t="n">
+        <v>2</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>きちんと</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D190" t="n">
+        <v>2</v>
+      </c>
+      <c r="E190" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>成功する（せいこうする）</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D191" t="n">
+        <v>2</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>下げる（さげる）</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>2</v>
+      </c>
+      <c r="C192" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>修正（しゅうせい）</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>2</v>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>じつに（実に）</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2</v>
+      </c>
+      <c r="E194" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>便利（べんり）</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2</v>
+      </c>
+      <c r="E195" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>出勤（しゅっきん）</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>2</v>
+      </c>
+      <c r="C196" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2</v>
+      </c>
+      <c r="E196" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>実行する（じっこうする）</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>2</v>
+      </c>
+      <c r="C197" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>信用（しんよう）</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>2</v>
+      </c>
+      <c r="C198" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2</v>
+      </c>
+      <c r="E198" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>弱める（よわめる）</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D199" t="n">
+        <v>2</v>
+      </c>
+      <c r="E199" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>収支（しゅうし）</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>2</v>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>割合（わりあい）</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>2</v>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>安心（あんしん）</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>しかも</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ますぐ</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>割れる（われる）</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>安全（あんぜん）</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>出発（しゅっぱつ）</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>すぐ</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>つい</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1</v>
+      </c>
+      <c r="E209" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>送る（おくる）</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>役割（やくわり）</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>病気（びょうき）</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>競争（きょうそう）</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>契約書（けいやくしょ）</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>いくつか</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>意見（いけん）</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>深める（ふかめる）</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>回る（まわる）</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D218" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>不健康（ふけんこう）</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>支出（ししゅつ）</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1</v>
+      </c>
+      <c r="C220" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>商品（しょうひん）</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>不安（ふあん）</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>負ける（まける）</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>もう</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>工業（こうぎょう）</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D225" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>いっぱい</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>1</v>
+      </c>
+      <c r="C226" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D226" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>壊れる（こわれる）</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>不丁寧な（ふていねいな）</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D228" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>欠勤（けっきん）</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>1</v>
+      </c>
+      <c r="C229" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D229" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>易しい（やさしい）</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>1</v>
+      </c>
+      <c r="C230" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ときどき</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>1</v>
+      </c>
+      <c r="C231" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>正確（せいかく）</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>1</v>
+      </c>
+      <c r="C232" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1</v>
+      </c>
+      <c r="E232" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>いずれ</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>1</v>
+      </c>
+      <c r="C233" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D233" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>脱出する（だっしゅつする）</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
+      <c r="C234" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>穏やか（おだやか）</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>1</v>
+      </c>
+      <c r="C235" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D235" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>農業（のうぎょう）</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>1</v>
+      </c>
+      <c r="C236" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>素敵（すてき）</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>1</v>
+      </c>
+      <c r="C237" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>運動（うんどう）</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>1</v>
+      </c>
+      <c r="C238" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D238" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>影響する（えいきょうする）</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>1</v>
+      </c>
+      <c r="C239" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1</v>
+      </c>
+      <c r="E239" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>進む（すすむ）</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>1</v>
+      </c>
+      <c r="C240" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>不適当（ふてきとう）</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>1</v>
+      </c>
+      <c r="C241" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D241" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>維持する（いじする）</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D242" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>休日（きゅうじつ）</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>1</v>
+      </c>
+      <c r="C243" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>不正確な（ふせいかくな）</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D244" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>簡単（かんたん）</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1</v>
+      </c>
+      <c r="E245" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>消える（きえる）</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>1</v>
+      </c>
+      <c r="C246" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D246" t="n">
+        <v>1</v>
+      </c>
+      <c r="E246" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>活発（かっぱつ）</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>1</v>
+      </c>
+      <c r="C247" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>調整する（ちょうせいする）</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>1</v>
+      </c>
+      <c r="C248" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D248" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>必要（ひつよう）</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>1</v>
+      </c>
+      <c r="C249" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D249" t="n">
+        <v>1</v>
+      </c>
+      <c r="E249" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>つまり</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>1</v>
+      </c>
+      <c r="C250" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D250" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>とにかく</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>1</v>
+      </c>
+      <c r="C251" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D251" t="n">
+        <v>1</v>
+      </c>
+      <c r="E251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>関わる（かかわる）</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>1</v>
+      </c>
+      <c r="C252" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D252" t="n">
+        <v>1</v>
+      </c>
+      <c r="E252" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>元気（げんき）</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>1</v>
+      </c>
+      <c r="C253" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D253" t="n">
+        <v>1</v>
+      </c>
+      <c r="E253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>高い（たかい）</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>1</v>
+      </c>
+      <c r="C254" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D254" t="n">
+        <v>1</v>
+      </c>
+      <c r="E254" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>折れる（おれる）</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D255" t="n">
+        <v>1</v>
+      </c>
+      <c r="E255" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ほんの</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>1</v>
+      </c>
+      <c r="C256" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D256" t="n">
+        <v>1</v>
+      </c>
+      <c r="E256" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>わざと</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>1</v>
+      </c>
+      <c r="C257" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D257" t="n">
+        <v>1</v>
+      </c>
+      <c r="E257" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>変化（へんか）</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>1</v>
+      </c>
+      <c r="C258" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D258" t="n">
+        <v>1</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>柔らかい（やわらかい）</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>1</v>
+      </c>
+      <c r="C259" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D259" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>成功（せいこう）</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>1</v>
+      </c>
+      <c r="C260" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D260" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>すでに</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>1</v>
+      </c>
+      <c r="C261" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D261" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>なぜなら</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>1</v>
+      </c>
+      <c r="C262" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D262" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>認識する（にんしきする）</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>1</v>
+      </c>
+      <c r="C263" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D263" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>そのため</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>1</v>
+      </c>
+      <c r="C264" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D264" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>利益（りえき）</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>1</v>
+      </c>
+      <c r="C265" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D265" t="n">
+        <v>1</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>処理（しょり）</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>1</v>
+      </c>
+      <c r="C266" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D266" t="n">
+        <v>1</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>判決（はんけつ）</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>1</v>
+      </c>
+      <c r="C267" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D267" t="n">
+        <v>1</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>調整（ちょうせい）</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>1</v>
+      </c>
+      <c r="C268" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D268" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>協力（きょうりょく）</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>1</v>
+      </c>
+      <c r="C269" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1</v>
+      </c>
+      <c r="E269" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>環境保護（かんきょうほご）</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>1</v>
+      </c>
+      <c r="C270" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>看護（かんご）</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>1</v>
+      </c>
+      <c r="C271" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>関係（かんけい）</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>1</v>
+      </c>
+      <c r="C272" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D272" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>もっとも</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>1</v>
+      </c>
+      <c r="C273" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D273" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>嫌い（きらい）</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>1</v>
+      </c>
+      <c r="C274" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>どんどん</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>1</v>
+      </c>
+      <c r="C275" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1</v>
+      </c>
+      <c r="E275" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>台風（たいふう）</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>1</v>
+      </c>
+      <c r="C276" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>早い（はやい）</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>1</v>
+      </c>
+      <c r="C277" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>渡す（わたす）</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>1</v>
+      </c>
+      <c r="C278" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1</v>
+      </c>
+      <c r="E278" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>変わる（かわる）</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>1</v>
+      </c>
+      <c r="C279" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D279" t="n">
+        <v>1</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>需要（じゅよう）</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>1</v>
+      </c>
+      <c r="C280" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D280" t="n">
+        <v>1</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>予約（よやく）</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>1</v>
+      </c>
+      <c r="C281" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>出る（でる）</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>1</v>
+      </c>
+      <c r="C282" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D282" t="n">
+        <v>1</v>
+      </c>
+      <c r="E282" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>解決策（かいけつさく）</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>1</v>
+      </c>
+      <c r="C283" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D283" t="n">
+        <v>1</v>
+      </c>
+      <c r="E283" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>下がる（さがる）</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>1</v>
+      </c>
+      <c r="C284" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D284" t="n">
+        <v>1</v>
+      </c>
+      <c r="E284" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>続ける（つづける）</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>1</v>
+      </c>
+      <c r="C285" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D285" t="n">
+        <v>1</v>
+      </c>
+      <c r="E285" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>1</v>
+      </c>
+      <c r="C286" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D286" t="n">
+        <v>1</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>さっぱり</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>1</v>
+      </c>
+      <c r="C287" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D287" t="n">
+        <v>1</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>昇進（しょうしん）</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>1</v>
+      </c>
+      <c r="C288" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D288" t="n">
+        <v>1</v>
+      </c>
+      <c r="E288" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>故障（こしょう）</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>1</v>
+      </c>
+      <c r="C289" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D289" t="n">
+        <v>1</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>勝つ（かつ）</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>1</v>
+      </c>
+      <c r="C290" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D290" t="n">
+        <v>1</v>
+      </c>
+      <c r="E290" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>親子（おやこ）</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>1</v>
+      </c>
+      <c r="C291" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D291" t="n">
+        <v>1</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>素敵な（すてきな）</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>1</v>
+      </c>
+      <c r="C292" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D292" t="n">
+        <v>1</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>合格（ごうかく）</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>1</v>
+      </c>
+      <c r="C293" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D293" t="n">
+        <v>1</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>会議（かいぎ）</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>1</v>
+      </c>
+      <c r="C294" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D294" t="n">
+        <v>1</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>冷やす（ひやす）</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>1</v>
+      </c>
+      <c r="C295" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D295" t="n">
+        <v>1</v>
+      </c>
+      <c r="E295" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>まさか</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>1</v>
+      </c>
+      <c r="C296" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D296" t="n">
+        <v>1</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>組合（くみあい）</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>1</v>
+      </c>
+      <c r="C297" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D297" t="n">
+        <v>1</v>
+      </c>
+      <c r="E297" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>美しい（うつくしい）</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>1</v>
+      </c>
+      <c r="C298" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D298" t="n">
+        <v>1</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>通る（とおる）</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>1</v>
+      </c>
+      <c r="C299" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D299" t="n">
+        <v>1</v>
+      </c>
+      <c r="E299" t="n">
         <v>1</v>
       </c>
     </row>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E299"/>
+  <dimension ref="A1:E399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,13 +454,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
@@ -549,16 +549,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -739,13 +739,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -758,13 +758,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -853,13 +853,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -872,13 +872,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -948,16 +948,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -986,13 +986,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1024,13 +1024,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1043,16 +1043,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
         <v>3</v>
@@ -1100,16 +1100,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
         <v>3</v>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
         <v>2</v>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
         <v>3</v>
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
         <v>2</v>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
         <v>2</v>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
         <v>2</v>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
@@ -1461,13 +1461,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -1480,16 +1480,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -1518,13 +1518,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
         <v>2</v>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
@@ -1556,13 +1556,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
         <v>2</v>
@@ -1594,13 +1594,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
         <v>4</v>
@@ -1632,13 +1632,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -1651,16 +1651,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -1689,13 +1689,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
         <v>2</v>
@@ -1708,13 +1708,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
         <v>2</v>
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -1803,16 +1803,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -1841,16 +1841,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -1860,16 +1860,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
         <v>2</v>
@@ -1898,13 +1898,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
         <v>1</v>
@@ -1936,13 +1936,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
         <v>4</v>
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
         <v>3</v>
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
         <v>3</v>
@@ -2015,13 +2015,13 @@
         <v>1</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
@@ -2050,13 +2050,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
         <v>5</v>
@@ -2088,16 +2088,16 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -2126,16 +2126,16 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
         <v>7</v>
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -2202,13 +2202,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E94" t="n">
         <v>4</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96" t="n">
         <v>2</v>
@@ -2259,16 +2259,16 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E97" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -2278,16 +2278,16 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -2297,16 +2297,16 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E101" t="n">
         <v>3</v>
@@ -2354,13 +2354,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" t="n">
         <v>8</v>
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E103" t="n">
         <v>2</v>
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E106" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107">
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E107" t="n">
         <v>5</v>
@@ -2468,13 +2468,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E108" t="n">
         <v>2</v>
@@ -2506,13 +2506,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
         <v>5</v>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E111" t="n">
         <v>2</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E113" t="n">
         <v>5</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E118" t="n">
         <v>3</v>
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E119" t="n">
         <v>1</v>
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E123" t="n">
         <v>5</v>
@@ -2775,13 +2775,13 @@
         <v>1</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E124" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E125" t="n">
         <v>4</v>
@@ -2832,13 +2832,13 @@
         <v>1</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
@@ -2851,13 +2851,13 @@
         <v>1</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E129" t="n">
         <v>2</v>
@@ -2965,13 +2965,13 @@
         <v>1</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135">
@@ -2981,13 +2981,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E135" t="n">
         <v>2</v>
@@ -3000,13 +3000,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E136" t="n">
         <v>5</v>
@@ -3022,13 +3022,13 @@
         <v>1</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138">
@@ -3060,13 +3060,13 @@
         <v>1</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -3076,13 +3076,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E140" t="n">
         <v>4</v>
@@ -3095,13 +3095,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E141" t="n">
         <v>2</v>
@@ -3193,13 +3193,13 @@
         <v>1</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E146" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147">
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E149" t="n">
         <v>3</v>
@@ -3269,13 +3269,13 @@
         <v>1</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
@@ -3285,13 +3285,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E151" t="n">
         <v>6</v>
@@ -3342,13 +3342,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E154" t="n">
         <v>5</v>
@@ -3364,13 +3364,13 @@
         <v>1</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
@@ -3380,13 +3380,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E156" t="n">
         <v>2</v>
@@ -3418,13 +3418,13 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E158" t="n">
         <v>4</v>
@@ -3475,13 +3475,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E161" t="n">
         <v>2</v>
@@ -3494,13 +3494,13 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E162" t="n">
         <v>3</v>
@@ -3513,13 +3513,13 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E163" t="n">
         <v>4</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E165" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166">
@@ -3570,13 +3570,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E166" t="n">
         <v>3</v>
@@ -3608,13 +3608,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E168" t="n">
         <v>3</v>
@@ -3646,13 +3646,13 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E170" t="n">
         <v>2</v>
@@ -3722,13 +3722,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E174" t="n">
         <v>2</v>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E175" t="n">
         <v>8</v>
@@ -3779,13 +3779,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E177" t="n">
         <v>3</v>
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E179" t="n">
         <v>8</v>
@@ -3836,13 +3836,13 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E180" t="n">
         <v>6</v>
@@ -3855,13 +3855,13 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E181" t="n">
         <v>2</v>
@@ -3874,13 +3874,13 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E182" t="n">
         <v>2</v>
@@ -3896,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184">
@@ -3931,13 +3931,13 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E185" t="n">
         <v>4</v>
@@ -3953,13 +3953,13 @@
         <v>1</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187">
@@ -3988,13 +3988,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E188" t="n">
         <v>2</v>
@@ -4026,13 +4026,13 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E190" t="n">
         <v>5</v>
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E191" t="n">
         <v>2</v>
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E194" t="n">
         <v>9</v>
@@ -4124,13 +4124,13 @@
         <v>1</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E195" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196">
@@ -4197,13 +4197,13 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E199" t="n">
         <v>4</v>
@@ -4254,13 +4254,13 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
@@ -4273,13 +4273,13 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E203" t="n">
         <v>2</v>
@@ -4295,13 +4295,13 @@
         <v>1</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -4314,13 +4314,13 @@
         <v>1</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E205" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206">
@@ -4330,13 +4330,13 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E206" t="n">
         <v>2</v>
@@ -4349,13 +4349,13 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E207" t="n">
         <v>1</v>
@@ -4368,13 +4368,13 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
@@ -4387,13 +4387,13 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E209" t="n">
         <v>2</v>
@@ -4406,13 +4406,13 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E210" t="n">
         <v>2</v>
@@ -4425,13 +4425,13 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E211" t="n">
         <v>1</v>
@@ -4444,13 +4444,13 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E212" t="n">
         <v>1</v>
@@ -4466,13 +4466,13 @@
         <v>1</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E213" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
@@ -4482,13 +4482,13 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E214" t="n">
         <v>1</v>
@@ -4501,13 +4501,13 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E215" t="n">
         <v>1</v>
@@ -4520,13 +4520,13 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E216" t="n">
         <v>1</v>
@@ -4542,13 +4542,13 @@
         <v>1</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218">
@@ -4561,13 +4561,13 @@
         <v>1</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E218" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219">
@@ -4577,13 +4577,13 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E219" t="n">
         <v>2</v>
@@ -4596,13 +4596,13 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E220" t="n">
         <v>1</v>
@@ -4615,13 +4615,13 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E221" t="n">
         <v>0</v>
@@ -4637,13 +4637,13 @@
         <v>1</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -4653,13 +4653,13 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E223" t="n">
         <v>2</v>
@@ -4672,13 +4672,13 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E224" t="n">
         <v>0</v>
@@ -4691,13 +4691,13 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E225" t="n">
         <v>0</v>
@@ -4713,13 +4713,13 @@
         <v>1</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -4732,13 +4732,13 @@
         <v>1</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -4748,13 +4748,13 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E228" t="n">
         <v>3</v>
@@ -4767,13 +4767,13 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E229" t="n">
         <v>1</v>
@@ -4786,13 +4786,13 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E230" t="n">
         <v>2</v>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E231" t="n">
         <v>1</v>
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E232" t="n">
         <v>2</v>
@@ -4846,13 +4846,13 @@
         <v>1</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -4865,13 +4865,13 @@
         <v>1</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E234" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="235">
@@ -4884,13 +4884,13 @@
         <v>1</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E235" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="236">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E236" t="n">
         <v>1</v>
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E237" t="n">
         <v>3</v>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E238" t="n">
         <v>1</v>
@@ -4957,13 +4957,13 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E239" t="n">
         <v>2</v>
@@ -4979,13 +4979,13 @@
         <v>1</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E241" t="n">
         <v>2</v>
@@ -5014,13 +5014,13 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E242" t="n">
         <v>2</v>
@@ -5033,13 +5033,13 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E243" t="n">
         <v>2</v>
@@ -5052,13 +5052,13 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E244" t="n">
         <v>2</v>
@@ -5071,13 +5071,13 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E245" t="n">
         <v>3</v>
@@ -5090,13 +5090,13 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E246" t="n">
         <v>3</v>
@@ -5112,13 +5112,13 @@
         <v>1</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E247" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248">
@@ -5128,13 +5128,13 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E248" t="n">
         <v>2</v>
@@ -5147,13 +5147,13 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E249" t="n">
         <v>1</v>
@@ -5169,13 +5169,13 @@
         <v>1</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -5185,13 +5185,13 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E251" t="n">
         <v>1</v>
@@ -5204,13 +5204,13 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E252" t="n">
         <v>3</v>
@@ -5223,13 +5223,13 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E253" t="n">
         <v>1</v>
@@ -5242,13 +5242,13 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E254" t="n">
         <v>1</v>
@@ -5264,13 +5264,13 @@
         <v>1</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -5283,13 +5283,13 @@
         <v>1</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E256" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="257">
@@ -5302,13 +5302,13 @@
         <v>1</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E257" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258">
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E258" t="n">
         <v>0</v>
@@ -5340,13 +5340,13 @@
         <v>1</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E259" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="260">
@@ -5356,13 +5356,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E260" t="n">
         <v>0</v>
@@ -5378,13 +5378,13 @@
         <v>1</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
@@ -5394,13 +5394,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E262" t="n">
         <v>1</v>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E263" t="n">
         <v>0</v>
@@ -5432,13 +5432,13 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E264" t="n">
         <v>0</v>
@@ -5451,13 +5451,13 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E265" t="n">
         <v>1</v>
@@ -5470,13 +5470,13 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E266" t="n">
         <v>1</v>
@@ -5489,13 +5489,13 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E267" t="n">
         <v>1</v>
@@ -5508,13 +5508,13 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E268" t="n">
         <v>0</v>
@@ -5530,13 +5530,13 @@
         <v>1</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -5546,13 +5546,13 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E270" t="n">
         <v>1</v>
@@ -5565,13 +5565,13 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E271" t="n">
         <v>2</v>
@@ -5584,13 +5584,13 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E272" t="n">
         <v>1</v>
@@ -5606,13 +5606,13 @@
         <v>1</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D273" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E273" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="274">
@@ -5622,13 +5622,13 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
@@ -5641,13 +5641,13 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E275" t="n">
         <v>2</v>
@@ -5660,13 +5660,13 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E276" t="n">
         <v>1</v>
@@ -5679,13 +5679,13 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
@@ -5698,13 +5698,13 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E278" t="n">
         <v>1</v>
@@ -5717,13 +5717,13 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E279" t="n">
         <v>1</v>
@@ -5739,13 +5739,13 @@
         <v>1</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -5758,13 +5758,13 @@
         <v>1</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E282" t="n">
         <v>1</v>
@@ -5793,13 +5793,13 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E283" t="n">
         <v>1</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E284" t="n">
         <v>1</v>
@@ -5831,13 +5831,13 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E285" t="n">
         <v>1</v>
@@ -5850,13 +5850,13 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E286" t="n">
         <v>0</v>
@@ -5869,13 +5869,13 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E287" t="n">
         <v>0</v>
@@ -5888,13 +5888,13 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E288" t="n">
         <v>2</v>
@@ -5910,13 +5910,13 @@
         <v>1</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
@@ -5926,13 +5926,13 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E290" t="n">
         <v>2</v>
@@ -5945,13 +5945,13 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E291" t="n">
         <v>1</v>
@@ -5967,13 +5967,13 @@
         <v>1</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D292" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E292" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -5983,13 +5983,13 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E293" t="n">
         <v>1</v>
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E294" t="n">
         <v>1</v>
@@ -6024,13 +6024,13 @@
         <v>1</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E295" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="296">
@@ -6040,13 +6040,13 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E296" t="n">
         <v>1</v>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E297" t="n">
         <v>1</v>
@@ -6078,13 +6078,13 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E298" t="n">
         <v>1</v>
@@ -6097,15 +6097,1915 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="D299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E299" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>立派（りっぱ）</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>1</v>
+      </c>
+      <c r="C300" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D300" t="n">
+        <v>1</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>保存（ほぞん）</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>1</v>
+      </c>
+      <c r="C301" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D301" t="n">
+        <v>1</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>寒い（さむい）</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>1</v>
+      </c>
+      <c r="C302" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>楽しい（たのしい）</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>1</v>
+      </c>
+      <c r="C303" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D303" t="n">
+        <v>1</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>間違い（まちがい）</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>1</v>
+      </c>
+      <c r="C304" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D304" t="n">
+        <v>1</v>
+      </c>
+      <c r="E304" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>改善（かいぜん）</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>1</v>
+      </c>
+      <c r="C305" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D305" t="n">
+        <v>1</v>
+      </c>
+      <c r="E305" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>返す（かえす）</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>1</v>
+      </c>
+      <c r="C306" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D306" t="n">
+        <v>1</v>
+      </c>
+      <c r="E306" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>不明確（ふめいかく）</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>1</v>
+      </c>
+      <c r="C307" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D307" t="n">
+        <v>1</v>
+      </c>
+      <c r="E307" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>入学（にゅうがく）</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>1</v>
+      </c>
+      <c r="C308" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>かならず（必ず）</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>1</v>
+      </c>
+      <c r="C309" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D309" t="n">
+        <v>1</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>避ける（さける）</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>1</v>
+      </c>
+      <c r="C310" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D310" t="n">
+        <v>1</v>
+      </c>
+      <c r="E310" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>保つ（たもつ）</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>1</v>
+      </c>
+      <c r="C311" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D311" t="n">
+        <v>1</v>
+      </c>
+      <c r="E311" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>苦い（にがい）</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>1</v>
+      </c>
+      <c r="C312" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D312" t="n">
+        <v>1</v>
+      </c>
+      <c r="E312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>機関（きかん）</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>1</v>
+      </c>
+      <c r="C313" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>準備（じゅんび）</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>1</v>
+      </c>
+      <c r="C314" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1</v>
+      </c>
+      <c r="E314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>入社（にゅうしゃ）</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>1</v>
+      </c>
+      <c r="C315" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D315" t="n">
+        <v>1</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>残業（ざんぎょう）</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>1</v>
+      </c>
+      <c r="C316" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D316" t="n">
+        <v>1</v>
+      </c>
+      <c r="E316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>たまたま</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>1</v>
+      </c>
+      <c r="C317" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D317" t="n">
+        <v>1</v>
+      </c>
+      <c r="E317" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>受け取る（うけとる）</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>1</v>
+      </c>
+      <c r="C318" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D318" t="n">
+        <v>1</v>
+      </c>
+      <c r="E318" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>快適（かいてき）</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>1</v>
+      </c>
+      <c r="C319" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D319" t="n">
+        <v>1</v>
+      </c>
+      <c r="E319" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>経由（けいゆ）</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>1</v>
+      </c>
+      <c r="C320" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D320" t="n">
+        <v>1</v>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>緊張（きんちょう）</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>1</v>
+      </c>
+      <c r="C321" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D321" t="n">
+        <v>1</v>
+      </c>
+      <c r="E321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>要求（ようきゅう）</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>1</v>
+      </c>
+      <c r="C322" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D322" t="n">
+        <v>1</v>
+      </c>
+      <c r="E322" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>適切（てきせつ）</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>1</v>
+      </c>
+      <c r="C323" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D323" t="n">
+        <v>1</v>
+      </c>
+      <c r="E323" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>自由（じゆう）</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>1</v>
+      </c>
+      <c r="C324" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D324" t="n">
+        <v>1</v>
+      </c>
+      <c r="E324" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>ちょうど</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>1</v>
+      </c>
+      <c r="C325" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D325" t="n">
+        <v>1</v>
+      </c>
+      <c r="E325" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>広がる（ひろがる）</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>1</v>
+      </c>
+      <c r="C326" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D326" t="n">
+        <v>1</v>
+      </c>
+      <c r="E326" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>対立（たいりつ）</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>1</v>
+      </c>
+      <c r="C327" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D327" t="n">
+        <v>1</v>
+      </c>
+      <c r="E327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>曲げる（まげる）</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>1</v>
+      </c>
+      <c r="C328" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D328" t="n">
+        <v>1</v>
+      </c>
+      <c r="E328" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>やっぱり</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>1</v>
+      </c>
+      <c r="C329" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D329" t="n">
+        <v>1</v>
+      </c>
+      <c r="E329" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>発達する（はったつする）</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>1</v>
+      </c>
+      <c r="C330" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D330" t="n">
+        <v>1</v>
+      </c>
+      <c r="E330" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>ところで</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>1</v>
+      </c>
+      <c r="C331" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D331" t="n">
+        <v>1</v>
+      </c>
+      <c r="E331" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>滞在（たいざい）</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>1</v>
+      </c>
+      <c r="C332" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D332" t="n">
+        <v>1</v>
+      </c>
+      <c r="E332" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>目標（もくひょう）</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>1</v>
+      </c>
+      <c r="C333" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D333" t="n">
+        <v>1</v>
+      </c>
+      <c r="E333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>なおかつ</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>1</v>
+      </c>
+      <c r="C334" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D334" t="n">
+        <v>1</v>
+      </c>
+      <c r="E334" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>例えば</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>1</v>
+      </c>
+      <c r="C335" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D335" t="n">
+        <v>1</v>
+      </c>
+      <c r="E335" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>いっしょうけんめい</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>1</v>
+      </c>
+      <c r="C336" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D336" t="n">
+        <v>1</v>
+      </c>
+      <c r="E336" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>管理（かんり）</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>1</v>
+      </c>
+      <c r="C337" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D337" t="n">
+        <v>1</v>
+      </c>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>不完全（ふかんぜん）</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>1</v>
+      </c>
+      <c r="C338" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D338" t="n">
+        <v>1</v>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>救助（きゅうじょ）</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>1</v>
+      </c>
+      <c r="C339" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D339" t="n">
+        <v>1</v>
+      </c>
+      <c r="E339" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>招待（しょうたい）</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>1</v>
+      </c>
+      <c r="C340" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D340" t="n">
+        <v>1</v>
+      </c>
+      <c r="E340" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>在庫（ざいこ）</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>1</v>
+      </c>
+      <c r="C341" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D341" t="n">
+        <v>1</v>
+      </c>
+      <c r="E341" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>まだ</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>1</v>
+      </c>
+      <c r="C342" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D342" t="n">
+        <v>1</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>上級者（じょうきゅうしゃ）</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>1</v>
+      </c>
+      <c r="C343" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D343" t="n">
+        <v>1</v>
+      </c>
+      <c r="E343" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>捕まる（つかまる）</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>1</v>
+      </c>
+      <c r="C344" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D344" t="n">
+        <v>1</v>
+      </c>
+      <c r="E344" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>宿題（しゅくだい）</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>1</v>
+      </c>
+      <c r="C345" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D345" t="n">
+        <v>1</v>
+      </c>
+      <c r="E345" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>渋滞（じゅうたい）</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>1</v>
+      </c>
+      <c r="C346" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D346" t="n">
+        <v>1</v>
+      </c>
+      <c r="E346" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>表す（あらわす）</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>1</v>
+      </c>
+      <c r="C347" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D347" t="n">
+        <v>1</v>
+      </c>
+      <c r="E347" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>議会（ぎかい）</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>1</v>
+      </c>
+      <c r="C348" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D348" t="n">
+        <v>1</v>
+      </c>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>不運（ふうん）</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>1</v>
+      </c>
+      <c r="C349" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D349" t="n">
+        <v>1</v>
+      </c>
+      <c r="E349" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>飛行機（ひこうき）</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>1</v>
+      </c>
+      <c r="C350" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D350" t="n">
+        <v>1</v>
+      </c>
+      <c r="E350" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>テーブル</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>1</v>
+      </c>
+      <c r="C351" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D351" t="n">
+        <v>1</v>
+      </c>
+      <c r="E351" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>明日（あした）</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>1</v>
+      </c>
+      <c r="C352" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D352" t="n">
+        <v>1</v>
+      </c>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>赤（あか）</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>1</v>
+      </c>
+      <c r="C353" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D353" t="n">
+        <v>1</v>
+      </c>
+      <c r="E353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>水曜日（すいようび）</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>1</v>
+      </c>
+      <c r="C354" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D354" t="n">
+        <v>1</v>
+      </c>
+      <c r="E354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>金曜日（きんようび）</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>1</v>
+      </c>
+      <c r="C355" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D355" t="n">
+        <v>1</v>
+      </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>猫（ねこ）</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>1</v>
+      </c>
+      <c r="C356" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D356" t="n">
+        <v>1</v>
+      </c>
+      <c r="E356" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>九月（くがつ）</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>1</v>
+      </c>
+      <c r="C357" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D357" t="n">
+        <v>1</v>
+      </c>
+      <c r="E357" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>口（くち）</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>1</v>
+      </c>
+      <c r="C358" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D358" t="n">
+        <v>1</v>
+      </c>
+      <c r="E358" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>十一月（じゅういちがつ）</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>1</v>
+      </c>
+      <c r="C359" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D359" t="n">
+        <v>1</v>
+      </c>
+      <c r="E359" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>ご飯（ごはん）</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>1</v>
+      </c>
+      <c r="C360" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D360" t="n">
+        <v>1</v>
+      </c>
+      <c r="E360" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>四月（しがつ）</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>1</v>
+      </c>
+      <c r="C361" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D361" t="n">
+        <v>1</v>
+      </c>
+      <c r="E361" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>会社（かいしゃ）</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>1</v>
+      </c>
+      <c r="C362" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D362" t="n">
+        <v>1</v>
+      </c>
+      <c r="E362" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>茶色（ちゃいろ）</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>1</v>
+      </c>
+      <c r="C363" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D363" t="n">
+        <v>1</v>
+      </c>
+      <c r="E363" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>父（ちち）</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>1</v>
+      </c>
+      <c r="C364" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D364" t="n">
+        <v>1</v>
+      </c>
+      <c r="E364" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>寿司（すし）</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>1</v>
+      </c>
+      <c r="C365" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D365" t="n">
+        <v>1</v>
+      </c>
+      <c r="E365" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>山（やま）</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>1</v>
+      </c>
+      <c r="C366" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D366" t="n">
+        <v>1</v>
+      </c>
+      <c r="E366" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>刺身（さしみ）</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>1</v>
+      </c>
+      <c r="C367" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D367" t="n">
+        <v>1</v>
+      </c>
+      <c r="E367" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>公園（こうえん）</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>1</v>
+      </c>
+      <c r="C368" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D368" t="n">
+        <v>1</v>
+      </c>
+      <c r="E368" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>水（みず）</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>1</v>
+      </c>
+      <c r="C369" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D369" t="n">
+        <v>1</v>
+      </c>
+      <c r="E369" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>海（うみ）</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>1</v>
+      </c>
+      <c r="C370" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D370" t="n">
+        <v>1</v>
+      </c>
+      <c r="E370" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>足（あし）</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>1</v>
+      </c>
+      <c r="C371" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D371" t="n">
+        <v>1</v>
+      </c>
+      <c r="E371" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>八月（はちがつ）</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>1</v>
+      </c>
+      <c r="C372" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D372" t="n">
+        <v>1</v>
+      </c>
+      <c r="E372" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>日曜日（にちようび）</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>1</v>
+      </c>
+      <c r="C373" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D373" t="n">
+        <v>1</v>
+      </c>
+      <c r="E373" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>紫（むらさき）</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>1</v>
+      </c>
+      <c r="C374" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D374" t="n">
+        <v>1</v>
+      </c>
+      <c r="E374" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>カレーライス</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>1</v>
+      </c>
+      <c r="C375" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D375" t="n">
+        <v>1</v>
+      </c>
+      <c r="E375" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>下（した）</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>1</v>
+      </c>
+      <c r="C376" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D376" t="n">
+        <v>1</v>
+      </c>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>ゴミ箱（ごみばこ）</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>1</v>
+      </c>
+      <c r="C377" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D377" t="n">
+        <v>1</v>
+      </c>
+      <c r="E377" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>エアコン</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>1</v>
+      </c>
+      <c r="C378" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D378" t="n">
+        <v>1</v>
+      </c>
+      <c r="E378" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>左（ひだり）</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>1</v>
+      </c>
+      <c r="C379" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D379" t="n">
+        <v>1</v>
+      </c>
+      <c r="E379" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>財布（さいふ）</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>1</v>
+      </c>
+      <c r="C380" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D380" t="n">
+        <v>1</v>
+      </c>
+      <c r="E380" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>中（なか）</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>1</v>
+      </c>
+      <c r="C381" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D381" t="n">
+        <v>1</v>
+      </c>
+      <c r="E381" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>姉（あね）</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>1</v>
+      </c>
+      <c r="C382" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D382" t="n">
+        <v>1</v>
+      </c>
+      <c r="E382" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>緑（みどり）</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>1</v>
+      </c>
+      <c r="C383" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D383" t="n">
+        <v>1</v>
+      </c>
+      <c r="E383" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>黒（くろ）</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>1</v>
+      </c>
+      <c r="C384" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D384" t="n">
+        <v>1</v>
+      </c>
+      <c r="E384" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>弟（おとうと）</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>1</v>
+      </c>
+      <c r="C385" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D385" t="n">
+        <v>1</v>
+      </c>
+      <c r="E385" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>木（き）</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>1</v>
+      </c>
+      <c r="C386" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D386" t="n">
+        <v>1</v>
+      </c>
+      <c r="E386" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>鉛筆（えんぴつ）</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>1</v>
+      </c>
+      <c r="C387" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D387" t="n">
+        <v>1</v>
+      </c>
+      <c r="E387" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>目（め）</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>1</v>
+      </c>
+      <c r="C388" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D388" t="n">
+        <v>1</v>
+      </c>
+      <c r="E388" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>後ろ（うしろ）</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>1</v>
+      </c>
+      <c r="C389" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D389" t="n">
+        <v>1</v>
+      </c>
+      <c r="E389" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>五月（ごがつ）</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>1</v>
+      </c>
+      <c r="C390" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D390" t="n">
+        <v>1</v>
+      </c>
+      <c r="E390" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>三月（さんがつ）</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>1</v>
+      </c>
+      <c r="C391" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D391" t="n">
+        <v>1</v>
+      </c>
+      <c r="E391" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>魚（さかな）</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>1</v>
+      </c>
+      <c r="C392" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D392" t="n">
+        <v>1</v>
+      </c>
+      <c r="E392" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>一月（いちがつ）</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>1</v>
+      </c>
+      <c r="C393" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D393" t="n">
+        <v>1</v>
+      </c>
+      <c r="E393" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>十月（じゅうがつ）</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>1</v>
+      </c>
+      <c r="C394" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D394" t="n">
+        <v>1</v>
+      </c>
+      <c r="E394" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>駅（えき）</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>1</v>
+      </c>
+      <c r="C395" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D395" t="n">
+        <v>1</v>
+      </c>
+      <c r="E395" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>上（うえ）</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>1</v>
+      </c>
+      <c r="C396" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D396" t="n">
+        <v>1</v>
+      </c>
+      <c r="E396" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>本（ほん）</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>1</v>
+      </c>
+      <c r="C397" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D397" t="n">
+        <v>1</v>
+      </c>
+      <c r="E397" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>白（しろ）</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>1</v>
+      </c>
+      <c r="C398" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D398" t="n">
+        <v>1</v>
+      </c>
+      <c r="E398" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>朝（あさ）</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>1</v>
+      </c>
+      <c r="C399" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D399" t="n">
+        <v>1</v>
+      </c>
+      <c r="E399" t="n">
         <v>1</v>
       </c>
     </row>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E399"/>
+  <dimension ref="A1:E499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1214,13 +1214,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -1483,13 +1483,13 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
         <v>2</v>
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
         <v>7</v>
@@ -1806,13 +1806,13 @@
         <v>1</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -1844,13 +1844,13 @@
         <v>1</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -1860,13 +1860,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
         <v>5</v>
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E84" t="n">
         <v>9</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
         <v>4</v>
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
         <v>4</v>
@@ -2262,13 +2262,13 @@
         <v>1</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E97" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E98" t="n">
         <v>5</v>
@@ -2297,13 +2297,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E99" t="n">
         <v>4</v>
@@ -2319,13 +2319,13 @@
         <v>1</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E106" t="n">
         <v>11</v>
@@ -2772,13 +2772,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E124" t="n">
         <v>6</v>
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E127" t="n">
         <v>4</v>
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E128" t="n">
         <v>2</v>
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E134" t="n">
         <v>5</v>
@@ -3022,13 +3022,13 @@
         <v>1</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E137" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138">
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E139" t="n">
         <v>3</v>
@@ -3190,13 +3190,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E146" t="n">
         <v>6</v>
@@ -3266,13 +3266,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E150" t="n">
         <v>3</v>
@@ -3361,13 +3361,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E155" t="n">
         <v>4</v>
@@ -3551,13 +3551,13 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E165" t="n">
         <v>6</v>
@@ -3896,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E183" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184">
@@ -3953,13 +3953,13 @@
         <v>1</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E186" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="187">
@@ -4121,13 +4121,13 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D195" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E195" t="n">
         <v>5</v>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E204" t="n">
         <v>1</v>
@@ -4311,13 +4311,13 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E205" t="n">
         <v>4</v>
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E213" t="n">
         <v>4</v>
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E217" t="n">
         <v>3</v>
@@ -4561,13 +4561,13 @@
         <v>1</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E218" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="219">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E222" t="n">
         <v>1</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E226" t="n">
         <v>3</v>
@@ -4729,13 +4729,13 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E227" t="n">
         <v>3</v>
@@ -4846,13 +4846,13 @@
         <v>1</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -4862,13 +4862,13 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E234" t="n">
         <v>4</v>
@@ -4884,13 +4884,13 @@
         <v>1</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E235" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="236">
@@ -4976,13 +4976,13 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E240" t="n">
         <v>3</v>
@@ -5112,13 +5112,13 @@
         <v>1</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D247" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E247" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248">
@@ -5169,13 +5169,13 @@
         <v>1</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -5261,13 +5261,13 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E255" t="n">
         <v>3</v>
@@ -5280,13 +5280,13 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E256" t="n">
         <v>4</v>
@@ -5302,13 +5302,13 @@
         <v>1</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D257" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E257" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="258">
@@ -5340,13 +5340,13 @@
         <v>1</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D259" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E259" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="260">
@@ -5378,13 +5378,13 @@
         <v>1</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D261" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E261" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="262">
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E269" t="n">
         <v>3</v>
@@ -5606,13 +5606,13 @@
         <v>1</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D273" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E273" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="274">
@@ -5739,13 +5739,13 @@
         <v>1</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281">
@@ -5755,13 +5755,13 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E281" t="n">
         <v>2</v>
@@ -5907,13 +5907,13 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E289" t="n">
         <v>1</v>
@@ -5964,13 +5964,13 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E292" t="n">
         <v>3</v>
@@ -6021,13 +6021,13 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D295" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E295" t="n">
         <v>4</v>
@@ -6119,13 +6119,13 @@
         <v>1</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E301" t="n">
         <v>0</v>
@@ -6157,13 +6157,13 @@
         <v>1</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -6173,13 +6173,13 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E303" t="n">
         <v>0</v>
@@ -6192,13 +6192,13 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E304" t="n">
         <v>2</v>
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E305" t="n">
         <v>2</v>
@@ -6233,13 +6233,13 @@
         <v>1</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D306" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D307" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E307" t="n">
         <v>2</v>
@@ -6268,13 +6268,13 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E308" t="n">
         <v>0</v>
@@ -6287,13 +6287,13 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D309" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E309" t="n">
         <v>0</v>
@@ -6309,13 +6309,13 @@
         <v>1</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D310" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E310" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="311">
@@ -6328,13 +6328,13 @@
         <v>1</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D311" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E311" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="312">
@@ -6344,13 +6344,13 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E312" t="n">
         <v>1</v>
@@ -6363,13 +6363,13 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E313" t="n">
         <v>1</v>
@@ -6382,13 +6382,13 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E314" t="n">
         <v>0</v>
@@ -6401,13 +6401,13 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E315" t="n">
         <v>1</v>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E316" t="n">
         <v>0</v>
@@ -6439,13 +6439,13 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D317" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E317" t="n">
         <v>1</v>
@@ -6458,13 +6458,13 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E318" t="n">
         <v>2</v>
@@ -6477,13 +6477,13 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D319" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E319" t="n">
         <v>3</v>
@@ -6496,13 +6496,13 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D320" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E320" t="n">
         <v>0</v>
@@ -6515,13 +6515,13 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E321" t="n">
         <v>1</v>
@@ -6534,13 +6534,13 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D322" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E322" t="n">
         <v>0</v>
@@ -6553,13 +6553,13 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D323" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E323" t="n">
         <v>2</v>
@@ -6572,13 +6572,13 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E324" t="n">
         <v>1</v>
@@ -6594,13 +6594,13 @@
         <v>1</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E325" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326">
@@ -6613,13 +6613,13 @@
         <v>1</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E326" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327">
@@ -6629,13 +6629,13 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E327" t="n">
         <v>0</v>
@@ -6648,13 +6648,13 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E328" t="n">
         <v>2</v>
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E329" t="n">
         <v>0</v>
@@ -6686,13 +6686,13 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E330" t="n">
         <v>2</v>
@@ -6708,13 +6708,13 @@
         <v>1</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -6727,13 +6727,13 @@
         <v>1</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -6743,13 +6743,13 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E333" t="n">
         <v>0</v>
@@ -6765,13 +6765,13 @@
         <v>1</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -6781,13 +6781,13 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E335" t="n">
         <v>0</v>
@@ -6800,13 +6800,13 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E336" t="n">
         <v>0</v>
@@ -6819,13 +6819,13 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E337" t="n">
         <v>0</v>
@@ -6841,13 +6841,13 @@
         <v>1</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
@@ -6860,13 +6860,13 @@
         <v>1</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D339" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E339" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="340">
@@ -6876,13 +6876,13 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E340" t="n">
         <v>1</v>
@@ -6895,13 +6895,13 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E341" t="n">
         <v>2</v>
@@ -6914,13 +6914,13 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E342" t="n">
         <v>0</v>
@@ -6933,13 +6933,13 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E343" t="n">
         <v>1</v>
@@ -6955,13 +6955,13 @@
         <v>1</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D344" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E344" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="345">
@@ -6971,13 +6971,13 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E345" t="n">
         <v>1</v>
@@ -6993,13 +6993,13 @@
         <v>1</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E346" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="347">
@@ -7012,13 +7012,13 @@
         <v>1</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E347" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="348">
@@ -7028,13 +7028,13 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E348" t="n">
         <v>0</v>
@@ -7047,13 +7047,13 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E349" t="n">
         <v>3</v>
@@ -7066,13 +7066,13 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E350" t="n">
         <v>1</v>
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E351" t="n">
         <v>1</v>
@@ -7104,13 +7104,13 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E352" t="n">
         <v>0</v>
@@ -7123,13 +7123,13 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E353" t="n">
         <v>0</v>
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E354" t="n">
         <v>0</v>
@@ -7161,13 +7161,13 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E355" t="n">
         <v>0</v>
@@ -7180,13 +7180,13 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D356" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E356" t="n">
         <v>1</v>
@@ -7199,13 +7199,13 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E357" t="n">
         <v>1</v>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E358" t="n">
         <v>3</v>
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E359" t="n">
         <v>0</v>
@@ -7256,13 +7256,13 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E360" t="n">
         <v>1</v>
@@ -7278,13 +7278,13 @@
         <v>1</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -7294,13 +7294,13 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E362" t="n">
         <v>0</v>
@@ -7313,13 +7313,13 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E363" t="n">
         <v>3</v>
@@ -7332,13 +7332,13 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E364" t="n">
         <v>1</v>
@@ -7351,13 +7351,13 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E365" t="n">
         <v>2</v>
@@ -7373,13 +7373,13 @@
         <v>1</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E366" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="367">
@@ -7389,13 +7389,13 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D367" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E367" t="n">
         <v>1</v>
@@ -7408,13 +7408,13 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E368" t="n">
         <v>0</v>
@@ -7427,13 +7427,13 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D369" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E369" t="n">
         <v>1</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E370" t="n">
         <v>1</v>
@@ -7468,13 +7468,13 @@
         <v>1</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -7484,13 +7484,13 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E372" t="n">
         <v>1</v>
@@ -7503,13 +7503,13 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E373" t="n">
         <v>1</v>
@@ -7525,13 +7525,13 @@
         <v>1</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D374" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E374" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375">
@@ -7541,13 +7541,13 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D375" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E375" t="n">
         <v>1</v>
@@ -7560,13 +7560,13 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E376" t="n">
         <v>0</v>
@@ -7579,13 +7579,13 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E377" t="n">
         <v>0</v>
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E378" t="n">
         <v>1</v>
@@ -7617,13 +7617,13 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D379" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E379" t="n">
         <v>0</v>
@@ -7636,13 +7636,13 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D380" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E380" t="n">
         <v>1</v>
@@ -7655,13 +7655,13 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D381" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E381" t="n">
         <v>1</v>
@@ -7674,13 +7674,13 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D382" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E382" t="n">
         <v>1</v>
@@ -7696,13 +7696,13 @@
         <v>1</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E383" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="384">
@@ -7712,13 +7712,13 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D384" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E384" t="n">
         <v>2</v>
@@ -7731,13 +7731,13 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E385" t="n">
         <v>0</v>
@@ -7750,13 +7750,13 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D386" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E386" t="n">
         <v>0</v>
@@ -7769,13 +7769,13 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D387" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E387" t="n">
         <v>1</v>
@@ -7791,13 +7791,13 @@
         <v>1</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D388" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D389" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E389" t="n">
         <v>2</v>
@@ -7829,13 +7829,13 @@
         <v>1</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D390" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E390" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -7845,13 +7845,13 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D391" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E391" t="n">
         <v>0</v>
@@ -7864,13 +7864,13 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D392" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E392" t="n">
         <v>3</v>
@@ -7883,13 +7883,13 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E393" t="n">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E394" t="n">
         <v>0</v>
@@ -7921,13 +7921,13 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E395" t="n">
         <v>0</v>
@@ -7943,13 +7943,13 @@
         <v>1</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D396" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -7959,13 +7959,13 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E397" t="n">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E398" t="n">
         <v>2</v>
@@ -7997,16 +7997,1916 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="D399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E399" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>人気（にんき）</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>1</v>
+      </c>
+      <c r="C400" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D400" t="n">
+        <v>1</v>
+      </c>
+      <c r="E400" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>説明（せつめい）</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>1</v>
+      </c>
+      <c r="C401" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D401" t="n">
+        <v>1</v>
+      </c>
+      <c r="E401" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>開発（かいはつ）</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>1</v>
+      </c>
+      <c r="C402" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D402" t="n">
+        <v>1</v>
+      </c>
+      <c r="E402" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>延期（えんき）</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>1</v>
+      </c>
+      <c r="C403" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D403" t="n">
+        <v>1</v>
+      </c>
+      <c r="E403" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>条約（じょうやく）</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>1</v>
+      </c>
+      <c r="C404" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D404" t="n">
+        <v>1</v>
+      </c>
+      <c r="E404" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>選挙（せんきょ）</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>1</v>
+      </c>
+      <c r="C405" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D405" t="n">
+        <v>1</v>
+      </c>
+      <c r="E405" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>指導（しどう）</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>1</v>
+      </c>
+      <c r="C406" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D406" t="n">
+        <v>1</v>
+      </c>
+      <c r="E406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>初心者（しょしんしゃ）</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>1</v>
+      </c>
+      <c r="C407" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D407" t="n">
+        <v>1</v>
+      </c>
+      <c r="E407" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>多い（おおい）</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>1</v>
+      </c>
+      <c r="C408" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D408" t="n">
+        <v>1</v>
+      </c>
+      <c r="E408" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>確認する（かくにんする）</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>1</v>
+      </c>
+      <c r="C409" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D409" t="n">
+        <v>1</v>
+      </c>
+      <c r="E409" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>ほぼ</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>1</v>
+      </c>
+      <c r="C410" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D410" t="n">
+        <v>1</v>
+      </c>
+      <c r="E410" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>隠れる（かくれる）</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>1</v>
+      </c>
+      <c r="C411" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D411" t="n">
+        <v>1</v>
+      </c>
+      <c r="E411" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>昨日（きのう）</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>1</v>
+      </c>
+      <c r="C412" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D412" t="n">
+        <v>1</v>
+      </c>
+      <c r="E412" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>許可（きょか）</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>1</v>
+      </c>
+      <c r="C413" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D413" t="n">
+        <v>1</v>
+      </c>
+      <c r="E413" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>進化する（しんかする）</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>1</v>
+      </c>
+      <c r="C414" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D414" t="n">
+        <v>1</v>
+      </c>
+      <c r="E414" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>冷たい（つめたい）</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>1</v>
+      </c>
+      <c r="C415" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D415" t="n">
+        <v>1</v>
+      </c>
+      <c r="E415" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>応募（おうぼ）</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>1</v>
+      </c>
+      <c r="C416" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D416" t="n">
+        <v>1</v>
+      </c>
+      <c r="E416" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>基本（きほん）</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>1</v>
+      </c>
+      <c r="C417" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D417" t="n">
+        <v>1</v>
+      </c>
+      <c r="E417" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>さらに</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>1</v>
+      </c>
+      <c r="C418" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D418" t="n">
+        <v>1</v>
+      </c>
+      <c r="E418" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>感じる（かんじる）</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>1</v>
+      </c>
+      <c r="C419" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D419" t="n">
+        <v>1</v>
+      </c>
+      <c r="E419" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>計画（けいかく）</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>1</v>
+      </c>
+      <c r="C420" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D420" t="n">
+        <v>1</v>
+      </c>
+      <c r="E420" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>避難（ひなん）</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>1</v>
+      </c>
+      <c r="C421" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D421" t="n">
+        <v>1</v>
+      </c>
+      <c r="E421" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>使用（しよう）</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>1</v>
+      </c>
+      <c r="C422" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D422" t="n">
+        <v>1</v>
+      </c>
+      <c r="E422" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>申請（しんせい）</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>1</v>
+      </c>
+      <c r="C423" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D423" t="n">
+        <v>1</v>
+      </c>
+      <c r="E423" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>消しゴム（けしごむ）</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>1</v>
+      </c>
+      <c r="C424" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D424" t="n">
+        <v>1</v>
+      </c>
+      <c r="E424" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>ぜったいに</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>1</v>
+      </c>
+      <c r="C425" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D425" t="n">
+        <v>1</v>
+      </c>
+      <c r="E425" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>汚い（きたない）</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>1</v>
+      </c>
+      <c r="C426" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D426" t="n">
+        <v>1</v>
+      </c>
+      <c r="E426" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>じつは（実は）</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>1</v>
+      </c>
+      <c r="C427" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D427" t="n">
+        <v>1</v>
+      </c>
+      <c r="E427" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>質問（しつもん）</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>1</v>
+      </c>
+      <c r="C428" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D428" t="n">
+        <v>1</v>
+      </c>
+      <c r="E428" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>危険（きけん）</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>1</v>
+      </c>
+      <c r="C429" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D429" t="n">
+        <v>1</v>
+      </c>
+      <c r="E429" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>悩む（なやむ）</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>1</v>
+      </c>
+      <c r="C430" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D430" t="n">
+        <v>1</v>
+      </c>
+      <c r="E430" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>有利（ゆうり）</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>1</v>
+      </c>
+      <c r="C431" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D431" t="n">
+        <v>1</v>
+      </c>
+      <c r="E431" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>利用（りよう）</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>1</v>
+      </c>
+      <c r="C432" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D432" t="n">
+        <v>1</v>
+      </c>
+      <c r="E432" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>温度（おんど）</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>1</v>
+      </c>
+      <c r="C433" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D433" t="n">
+        <v>1</v>
+      </c>
+      <c r="E433" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>気をつける（きをつける）</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>1</v>
+      </c>
+      <c r="C434" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D434" t="n">
+        <v>1</v>
+      </c>
+      <c r="E434" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>学ぶ（まなぶ）</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>1</v>
+      </c>
+      <c r="C435" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D435" t="n">
+        <v>1</v>
+      </c>
+      <c r="E435" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>うっかり</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>1</v>
+      </c>
+      <c r="C436" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D436" t="n">
+        <v>1</v>
+      </c>
+      <c r="E436" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>禁止（きんし）</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>1</v>
+      </c>
+      <c r="C437" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D437" t="n">
+        <v>1</v>
+      </c>
+      <c r="E437" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>年金（ねんきん）</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>1</v>
+      </c>
+      <c r="C438" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D438" t="n">
+        <v>1</v>
+      </c>
+      <c r="E438" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>症状（しょうじょう）</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>1</v>
+      </c>
+      <c r="C439" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D439" t="n">
+        <v>1</v>
+      </c>
+      <c r="E439" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>滞留（たいりゅう）</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>1</v>
+      </c>
+      <c r="C440" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D440" t="n">
+        <v>1</v>
+      </c>
+      <c r="E440" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>増やす（ふやす）</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>1</v>
+      </c>
+      <c r="C441" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D441" t="n">
+        <v>1</v>
+      </c>
+      <c r="E441" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>深まる（ふかまる）</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>1</v>
+      </c>
+      <c r="C442" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D442" t="n">
+        <v>1</v>
+      </c>
+      <c r="E442" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>価値（かち）</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>1</v>
+      </c>
+      <c r="C443" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D443" t="n">
+        <v>1</v>
+      </c>
+      <c r="E443" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>二月（にがつ）</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>1</v>
+      </c>
+      <c r="C444" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D444" t="n">
+        <v>1</v>
+      </c>
+      <c r="E444" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>大事（だいじ）</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>1</v>
+      </c>
+      <c r="C445" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D445" t="n">
+        <v>1</v>
+      </c>
+      <c r="E445" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>消す（けす）</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>1</v>
+      </c>
+      <c r="C446" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D446" t="n">
+        <v>1</v>
+      </c>
+      <c r="E446" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>被害者（ひがいしゃ）</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>1</v>
+      </c>
+      <c r="C447" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D447" t="n">
+        <v>1</v>
+      </c>
+      <c r="E447" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>高度（こうど）</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>1</v>
+      </c>
+      <c r="C448" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D448" t="n">
+        <v>1</v>
+      </c>
+      <c r="E448" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>それにしても</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>1</v>
+      </c>
+      <c r="C449" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D449" t="n">
+        <v>1</v>
+      </c>
+      <c r="E449" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>一方で（いっぽうで）</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>1</v>
+      </c>
+      <c r="C450" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D450" t="n">
+        <v>0</v>
+      </c>
+      <c r="E450" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>その上</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>1</v>
+      </c>
+      <c r="C451" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D451" t="n">
+        <v>0</v>
+      </c>
+      <c r="E451" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>交通（こうつう）</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>1</v>
+      </c>
+      <c r="C452" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D452" t="n">
+        <v>1</v>
+      </c>
+      <c r="E452" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>届け出（とどけで）</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>1</v>
+      </c>
+      <c r="C453" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D453" t="n">
+        <v>1</v>
+      </c>
+      <c r="E453" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>輸送（ゆそう）</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>1</v>
+      </c>
+      <c r="C454" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D454" t="n">
+        <v>1</v>
+      </c>
+      <c r="E454" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>高める（たかめる）</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>1</v>
+      </c>
+      <c r="C455" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D455" t="n">
+        <v>1</v>
+      </c>
+      <c r="E455" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>体験（たいけん）</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>1</v>
+      </c>
+      <c r="C456" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D456" t="n">
+        <v>1</v>
+      </c>
+      <c r="E456" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>無名（むめい）</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>1</v>
+      </c>
+      <c r="C457" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D457" t="n">
+        <v>1</v>
+      </c>
+      <c r="E457" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>特別（とくべつ）</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>1</v>
+      </c>
+      <c r="C458" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D458" t="n">
+        <v>1</v>
+      </c>
+      <c r="E458" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>もともと</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>1</v>
+      </c>
+      <c r="C459" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D459" t="n">
+        <v>0</v>
+      </c>
+      <c r="E459" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>運賃（うんちん）</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>1</v>
+      </c>
+      <c r="C460" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D460" t="n">
+        <v>1</v>
+      </c>
+      <c r="E460" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>法案（ほうあん）</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>1</v>
+      </c>
+      <c r="C461" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D461" t="n">
+        <v>1</v>
+      </c>
+      <c r="E461" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>育成（いくせい）</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>1</v>
+      </c>
+      <c r="C462" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D462" t="n">
+        <v>1</v>
+      </c>
+      <c r="E462" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>裁判（さいばん）</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>1</v>
+      </c>
+      <c r="C463" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D463" t="n">
+        <v>1</v>
+      </c>
+      <c r="E463" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>耳（みみ）</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>1</v>
+      </c>
+      <c r="C464" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D464" t="n">
+        <v>1</v>
+      </c>
+      <c r="E464" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>なるほど</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>1</v>
+      </c>
+      <c r="C465" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D465" t="n">
+        <v>0</v>
+      </c>
+      <c r="E465" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>多数（たすう）</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>1</v>
+      </c>
+      <c r="C466" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D466" t="n">
+        <v>1</v>
+      </c>
+      <c r="E466" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>不必要（ふひつよう）</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>1</v>
+      </c>
+      <c r="C467" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D467" t="n">
+        <v>1</v>
+      </c>
+      <c r="E467" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>続く（つづく）</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>1</v>
+      </c>
+      <c r="C468" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D468" t="n">
+        <v>1</v>
+      </c>
+      <c r="E468" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>監督する（かんとくする）</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>1</v>
+      </c>
+      <c r="C469" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D469" t="n">
+        <v>1</v>
+      </c>
+      <c r="E469" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>祖母（そぼ）</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>1</v>
+      </c>
+      <c r="C470" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D470" t="n">
+        <v>1</v>
+      </c>
+      <c r="E470" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>修理（しゅうり）</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>1</v>
+      </c>
+      <c r="C471" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D471" t="n">
+        <v>1</v>
+      </c>
+      <c r="E471" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>軽い（かるい）</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>1</v>
+      </c>
+      <c r="C472" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D472" t="n">
+        <v>1</v>
+      </c>
+      <c r="E472" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>残る（のこる）</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>1</v>
+      </c>
+      <c r="C473" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D473" t="n">
+        <v>1</v>
+      </c>
+      <c r="E473" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>美味しい（おいしい）</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>1</v>
+      </c>
+      <c r="C474" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D474" t="n">
+        <v>1</v>
+      </c>
+      <c r="E474" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>完全（かんぜん）</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>1</v>
+      </c>
+      <c r="C475" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D475" t="n">
+        <v>1</v>
+      </c>
+      <c r="E475" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>練習する（れんしゅうする）</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>1</v>
+      </c>
+      <c r="C476" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D476" t="n">
+        <v>1</v>
+      </c>
+      <c r="E476" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>通す（とおす）</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>1</v>
+      </c>
+      <c r="C477" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D477" t="n">
+        <v>1</v>
+      </c>
+      <c r="E477" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>速度（そくど）</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>1</v>
+      </c>
+      <c r="C478" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D478" t="n">
+        <v>1</v>
+      </c>
+      <c r="E478" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>崩す（くずす）</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>1</v>
+      </c>
+      <c r="C479" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D479" t="n">
+        <v>1</v>
+      </c>
+      <c r="E479" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>個人（こじん）</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>1</v>
+      </c>
+      <c r="C480" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D480" t="n">
+        <v>1</v>
+      </c>
+      <c r="E480" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>診断（しんだん）</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>1</v>
+      </c>
+      <c r="C481" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D481" t="n">
+        <v>1</v>
+      </c>
+      <c r="E481" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>家庭（かてい）</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>1</v>
+      </c>
+      <c r="C482" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D482" t="n">
+        <v>1</v>
+      </c>
+      <c r="E482" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>乗せる（のせる）</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>1</v>
+      </c>
+      <c r="C483" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D483" t="n">
+        <v>1</v>
+      </c>
+      <c r="E483" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>とうとう</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>1</v>
+      </c>
+      <c r="C484" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D484" t="n">
+        <v>0</v>
+      </c>
+      <c r="E484" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>賛成（さんせい）</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>1</v>
+      </c>
+      <c r="C485" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D485" t="n">
+        <v>1</v>
+      </c>
+      <c r="E485" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>散る（ちる）</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>1</v>
+      </c>
+      <c r="C486" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D486" t="n">
+        <v>1</v>
+      </c>
+      <c r="E486" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>評価する（ひょうかする）</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>1</v>
+      </c>
+      <c r="C487" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D487" t="n">
+        <v>1</v>
+      </c>
+      <c r="E487" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>確実（かくじつ）</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>1</v>
+      </c>
+      <c r="C488" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D488" t="n">
+        <v>1</v>
+      </c>
+      <c r="E488" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>貴重（きちょう）</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>1</v>
+      </c>
+      <c r="C489" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D489" t="n">
+        <v>1</v>
+      </c>
+      <c r="E489" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>降ろす（おろす）</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>1</v>
+      </c>
+      <c r="C490" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D490" t="n">
+        <v>1</v>
+      </c>
+      <c r="E490" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>入れる（いれる）</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>1</v>
+      </c>
+      <c r="C491" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D491" t="n">
+        <v>1</v>
+      </c>
+      <c r="E491" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>予定（よてい）</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>1</v>
+      </c>
+      <c r="C492" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D492" t="n">
+        <v>1</v>
+      </c>
+      <c r="E492" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>非常に（ひじょうに）</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>1</v>
+      </c>
+      <c r="C493" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D493" t="n">
+        <v>0</v>
+      </c>
+      <c r="E493" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>ほんとうに（本当に）</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>1</v>
+      </c>
+      <c r="C494" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D494" t="n">
+        <v>0</v>
+      </c>
+      <c r="E494" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>指導する（しどうする）</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>1</v>
+      </c>
+      <c r="C495" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D495" t="n">
+        <v>1</v>
+      </c>
+      <c r="E495" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>嬉しい（うれしい）</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>1</v>
+      </c>
+      <c r="C496" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D496" t="n">
+        <v>1</v>
+      </c>
+      <c r="E496" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>複雑（ふくざつ）</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>1</v>
+      </c>
+      <c r="C497" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D497" t="n">
+        <v>1</v>
+      </c>
+      <c r="E497" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>奪う（うばう）</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>1</v>
+      </c>
+      <c r="C498" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D498" t="n">
+        <v>1</v>
+      </c>
+      <c r="E498" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>課程（かてい）</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>1</v>
+      </c>
+      <c r="C499" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D499" t="n">
+        <v>1</v>
+      </c>
+      <c r="E499" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
